--- a/scada_stratified_500_seed42.xlsx
+++ b/scada_stratified_500_seed42.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Documents\File Pipeline-Analytica\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WEB-SKRIPSI\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
   </bookViews>
   <sheets>
     <sheet name="SCADA Sample" sheetId="1" r:id="rId1"/>
@@ -5613,12 +5613,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M501"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="19.375" customWidth="1"/>
     <col min="2" max="2" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5659,7 +5660,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -5700,7 +5701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -5741,7 +5742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -5782,7 +5783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -5823,7 +5824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -5864,7 +5865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -5905,7 +5906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -5946,7 +5947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -5987,7 +5988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -6028,7 +6029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -6069,7 +6070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -6110,7 +6111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -6151,7 +6152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -6192,7 +6193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -6233,7 +6234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -6274,7 +6275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -6315,7 +6316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -6356,7 +6357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -6397,7 +6398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -6438,7 +6439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -6479,7 +6480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>13</v>
       </c>
@@ -6520,7 +6521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -6561,7 +6562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>13</v>
       </c>
@@ -6602,7 +6603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -6643,7 +6644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>13</v>
       </c>
@@ -6684,7 +6685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -6725,7 +6726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>13</v>
       </c>
@@ -6766,7 +6767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -6807,7 +6808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>13</v>
       </c>
@@ -6848,7 +6849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -6889,7 +6890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>13</v>
       </c>
@@ -6930,7 +6931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>13</v>
       </c>
@@ -6971,7 +6972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>13</v>
       </c>
@@ -7012,7 +7013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>13</v>
       </c>
@@ -7053,7 +7054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>175</v>
       </c>
@@ -7094,7 +7095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>175</v>
       </c>
@@ -7135,7 +7136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>175</v>
       </c>
@@ -7176,7 +7177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>175</v>
       </c>
@@ -7217,7 +7218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>175</v>
       </c>
@@ -7258,7 +7259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>175</v>
       </c>
@@ -7299,7 +7300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>175</v>
       </c>
@@ -7340,7 +7341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>175</v>
       </c>
@@ -7381,7 +7382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>175</v>
       </c>
@@ -7422,7 +7423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>175</v>
       </c>
@@ -7463,7 +7464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>175</v>
       </c>
@@ -7504,7 +7505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>175</v>
       </c>
@@ -7545,7 +7546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>175</v>
       </c>
@@ -7586,7 +7587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>175</v>
       </c>
@@ -7627,7 +7628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>175</v>
       </c>
@@ -7668,7 +7669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>175</v>
       </c>
@@ -7709,7 +7710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>175</v>
       </c>
@@ -7750,7 +7751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>175</v>
       </c>
@@ -7791,7 +7792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>175</v>
       </c>
@@ -7832,7 +7833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>175</v>
       </c>
@@ -7873,7 +7874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>175</v>
       </c>
@@ -7914,7 +7915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>175</v>
       </c>
@@ -7955,7 +7956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>175</v>
       </c>
@@ -7996,7 +7997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>175</v>
       </c>
@@ -8037,7 +8038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>175</v>
       </c>
@@ -8078,7 +8079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>175</v>
       </c>
@@ -8119,7 +8120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>175</v>
       </c>
@@ -8160,7 +8161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>175</v>
       </c>
@@ -8201,7 +8202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>175</v>
       </c>
@@ -8242,7 +8243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>175</v>
       </c>
@@ -8283,7 +8284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>301</v>
       </c>
@@ -8324,7 +8325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>301</v>
       </c>
@@ -8365,7 +8366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>301</v>
       </c>
@@ -8406,7 +8407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>301</v>
       </c>
@@ -8447,7 +8448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>301</v>
       </c>
@@ -8488,7 +8489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>301</v>
       </c>
@@ -8529,7 +8530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>301</v>
       </c>
@@ -8570,7 +8571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>301</v>
       </c>
@@ -8611,7 +8612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>301</v>
       </c>
@@ -8652,7 +8653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>301</v>
       </c>
@@ -8693,7 +8694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>301</v>
       </c>
@@ -8734,7 +8735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>301</v>
       </c>
@@ -8775,7 +8776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>301</v>
       </c>
@@ -8816,7 +8817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>301</v>
       </c>
@@ -8857,7 +8858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>301</v>
       </c>
@@ -8898,7 +8899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>301</v>
       </c>
@@ -8939,7 +8940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>301</v>
       </c>
@@ -8980,7 +8981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>301</v>
       </c>
@@ -9021,7 +9022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>301</v>
       </c>
@@ -9062,7 +9063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>301</v>
       </c>
@@ -9103,7 +9104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>301</v>
       </c>
@@ -9144,7 +9145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>301</v>
       </c>
@@ -9185,7 +9186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>301</v>
       </c>
@@ -9226,7 +9227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>301</v>
       </c>
@@ -9267,7 +9268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>301</v>
       </c>
@@ -9308,7 +9309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>301</v>
       </c>
@@ -9349,7 +9350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>301</v>
       </c>
@@ -9390,7 +9391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>301</v>
       </c>
@@ -9431,7 +9432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>301</v>
       </c>
@@ -9472,7 +9473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>301</v>
       </c>
@@ -9513,7 +9514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>301</v>
       </c>
@@ -9554,7 +9555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>431</v>
       </c>
@@ -9595,7 +9596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>431</v>
       </c>
@@ -9636,7 +9637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>431</v>
       </c>
@@ -9677,7 +9678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>431</v>
       </c>
@@ -9718,7 +9719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>431</v>
       </c>
@@ -9759,7 +9760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>431</v>
       </c>
@@ -9800,7 +9801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>431</v>
       </c>
@@ -9841,7 +9842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>431</v>
       </c>
@@ -9882,7 +9883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>431</v>
       </c>
@@ -9923,7 +9924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>431</v>
       </c>
@@ -9964,7 +9965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>431</v>
       </c>
@@ -10005,7 +10006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>431</v>
       </c>
@@ -10046,7 +10047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>431</v>
       </c>
@@ -10087,7 +10088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>431</v>
       </c>
@@ -10128,7 +10129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>431</v>
       </c>
@@ -10169,7 +10170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>431</v>
       </c>
@@ -10210,7 +10211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>431</v>
       </c>
@@ -10251,7 +10252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>431</v>
       </c>
@@ -10292,7 +10293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>431</v>
       </c>
@@ -10333,7 +10334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>431</v>
       </c>
@@ -10374,7 +10375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>431</v>
       </c>
@@ -10415,7 +10416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>431</v>
       </c>
@@ -10456,7 +10457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>431</v>
       </c>
@@ -10497,7 +10498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>431</v>
       </c>
@@ -10538,7 +10539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>431</v>
       </c>
@@ -10579,7 +10580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>431</v>
       </c>
@@ -10620,7 +10621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>431</v>
       </c>
@@ -10661,7 +10662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>431</v>
       </c>
@@ -10702,7 +10703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>431</v>
       </c>
@@ -10743,7 +10744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>431</v>
       </c>
@@ -10784,7 +10785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>431</v>
       </c>
@@ -10825,7 +10826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>431</v>
       </c>
@@ -10866,7 +10867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>431</v>
       </c>
@@ -10907,7 +10908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>431</v>
       </c>
@@ -10948,7 +10949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>431</v>
       </c>
@@ -10989,7 +10990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>565</v>
       </c>
@@ -11030,7 +11031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>565</v>
       </c>
@@ -11071,7 +11072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>565</v>
       </c>
@@ -11112,7 +11113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>565</v>
       </c>
@@ -11153,7 +11154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>565</v>
       </c>
@@ -11194,7 +11195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>565</v>
       </c>
@@ -11235,7 +11236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>565</v>
       </c>
@@ -11276,7 +11277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>565</v>
       </c>
@@ -11317,7 +11318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>565</v>
       </c>
@@ -11358,7 +11359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>565</v>
       </c>
@@ -11399,7 +11400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>565</v>
       </c>
@@ -11440,7 +11441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>565</v>
       </c>
@@ -11481,7 +11482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>565</v>
       </c>
@@ -11522,7 +11523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>565</v>
       </c>
@@ -11563,7 +11564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>565</v>
       </c>
@@ -11604,7 +11605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>565</v>
       </c>
@@ -11645,7 +11646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>565</v>
       </c>
@@ -11686,7 +11687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>565</v>
       </c>
@@ -11727,7 +11728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>565</v>
       </c>
@@ -11768,7 +11769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>565</v>
       </c>
@@ -11809,7 +11810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>565</v>
       </c>
@@ -11850,7 +11851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>565</v>
       </c>
@@ -11891,7 +11892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>565</v>
       </c>
@@ -11932,7 +11933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>565</v>
       </c>
@@ -11973,7 +11974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>565</v>
       </c>
@@ -12014,7 +12015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>565</v>
       </c>
@@ -12055,7 +12056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>565</v>
       </c>
@@ -12096,7 +12097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>565</v>
       </c>
@@ -12137,7 +12138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>565</v>
       </c>
@@ -12178,7 +12179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>565</v>
       </c>
@@ -12219,7 +12220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>679</v>
       </c>
@@ -12260,7 +12261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>679</v>
       </c>
@@ -12301,7 +12302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>679</v>
       </c>
@@ -12342,7 +12343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>679</v>
       </c>
@@ -12383,7 +12384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>679</v>
       </c>
@@ -12424,7 +12425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>679</v>
       </c>
@@ -12465,7 +12466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>679</v>
       </c>
@@ -12506,7 +12507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>679</v>
       </c>
@@ -12547,7 +12548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>679</v>
       </c>
@@ -12588,7 +12589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>679</v>
       </c>
@@ -12629,7 +12630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>679</v>
       </c>
@@ -12670,7 +12671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>679</v>
       </c>
@@ -12711,7 +12712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>679</v>
       </c>
@@ -12752,7 +12753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>679</v>
       </c>
@@ -12793,7 +12794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>679</v>
       </c>
@@ -12834,7 +12835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>679</v>
       </c>
@@ -12875,7 +12876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>679</v>
       </c>
@@ -12916,7 +12917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>679</v>
       </c>
@@ -12957,7 +12958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>679</v>
       </c>
@@ -12998,7 +12999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>679</v>
       </c>
@@ -13039,7 +13040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>679</v>
       </c>
@@ -13080,7 +13081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>679</v>
       </c>
@@ -13121,7 +13122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>679</v>
       </c>
@@ -13162,7 +13163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>679</v>
       </c>
@@ -13203,7 +13204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>679</v>
       </c>
@@ -13244,7 +13245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>679</v>
       </c>
@@ -13285,7 +13286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>679</v>
       </c>
@@ -13326,7 +13327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>679</v>
       </c>
@@ -13367,7 +13368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>679</v>
       </c>
@@ -13408,7 +13409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>679</v>
       </c>
@@ -13449,7 +13450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>790</v>
       </c>
@@ -13490,7 +13491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>790</v>
       </c>
@@ -13531,7 +13532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>790</v>
       </c>
@@ -13572,7 +13573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>790</v>
       </c>
@@ -13613,7 +13614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>790</v>
       </c>
@@ -13654,7 +13655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>790</v>
       </c>
@@ -13695,7 +13696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>790</v>
       </c>
@@ -13736,7 +13737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>790</v>
       </c>
@@ -13777,7 +13778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>790</v>
       </c>
@@ -13818,7 +13819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>790</v>
       </c>
@@ -13859,7 +13860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>790</v>
       </c>
@@ -13900,7 +13901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>790</v>
       </c>
@@ -13941,7 +13942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>790</v>
       </c>
@@ -13982,7 +13983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>790</v>
       </c>
@@ -14023,7 +14024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>790</v>
       </c>
@@ -14064,7 +14065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>790</v>
       </c>
@@ -14105,7 +14106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>790</v>
       </c>
@@ -14146,7 +14147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>790</v>
       </c>
@@ -14187,7 +14188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>790</v>
       </c>
@@ -14228,7 +14229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>790</v>
       </c>
@@ -14269,7 +14270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>790</v>
       </c>
@@ -14310,7 +14311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>790</v>
       </c>
@@ -14351,7 +14352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>790</v>
       </c>
@@ -14392,7 +14393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>872</v>
       </c>
@@ -14433,7 +14434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>872</v>
       </c>
@@ -14474,7 +14475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>872</v>
       </c>
@@ -14515,7 +14516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>872</v>
       </c>
@@ -14556,7 +14557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>872</v>
       </c>
@@ -14597,7 +14598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>872</v>
       </c>
@@ -14638,7 +14639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>872</v>
       </c>
@@ -14679,7 +14680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>872</v>
       </c>
@@ -14720,7 +14721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>872</v>
       </c>
@@ -14761,7 +14762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>872</v>
       </c>
@@ -14802,7 +14803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>872</v>
       </c>
@@ -14843,7 +14844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>872</v>
       </c>
@@ -14884,7 +14885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>872</v>
       </c>
@@ -14925,7 +14926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>872</v>
       </c>
@@ -14966,7 +14967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>872</v>
       </c>
@@ -15007,7 +15008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>872</v>
       </c>
@@ -15048,7 +15049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>872</v>
       </c>
@@ -15089,7 +15090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>872</v>
       </c>
@@ -15130,7 +15131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>872</v>
       </c>
@@ -15171,7 +15172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>872</v>
       </c>
@@ -15212,7 +15213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>872</v>
       </c>
@@ -15253,7 +15254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>872</v>
       </c>
@@ -15294,7 +15295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>872</v>
       </c>
@@ -15335,7 +15336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>872</v>
       </c>
@@ -15376,7 +15377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>872</v>
       </c>
@@ -15417,7 +15418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>872</v>
       </c>
@@ -15458,7 +15459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>872</v>
       </c>
@@ -15499,7 +15500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>872</v>
       </c>
@@ -15540,7 +15541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>976</v>
       </c>
@@ -15581,7 +15582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>976</v>
       </c>
@@ -15622,7 +15623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>976</v>
       </c>
@@ -15663,7 +15664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>976</v>
       </c>
@@ -15704,7 +15705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>976</v>
       </c>
@@ -15745,7 +15746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>976</v>
       </c>
@@ -15786,7 +15787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>976</v>
       </c>
@@ -15827,7 +15828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>976</v>
       </c>
@@ -15868,7 +15869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>976</v>
       </c>
@@ -15909,7 +15910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>976</v>
       </c>
@@ -15950,7 +15951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>976</v>
       </c>
@@ -15991,7 +15992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>976</v>
       </c>
@@ -16032,7 +16033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>976</v>
       </c>
@@ -16073,7 +16074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>976</v>
       </c>
@@ -16114,7 +16115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>976</v>
       </c>
@@ -16155,7 +16156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>976</v>
       </c>
@@ -16196,7 +16197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>976</v>
       </c>
@@ -16237,7 +16238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>976</v>
       </c>
@@ -16278,7 +16279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>976</v>
       </c>
@@ -16319,7 +16320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>976</v>
       </c>
@@ -16360,7 +16361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>976</v>
       </c>
@@ -16401,7 +16402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>976</v>
       </c>
@@ -16442,7 +16443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>976</v>
       </c>
@@ -16483,7 +16484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>976</v>
       </c>
@@ -16524,7 +16525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>976</v>
       </c>
@@ -16565,7 +16566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>976</v>
       </c>
@@ -16606,7 +16607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>976</v>
       </c>
@@ -16647,7 +16648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>976</v>
       </c>
@@ -16688,7 +16689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>976</v>
       </c>
@@ -16729,7 +16730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>976</v>
       </c>
@@ -16770,7 +16771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>976</v>
       </c>
@@ -16811,7 +16812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>1089</v>
       </c>
@@ -16852,7 +16853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>1089</v>
       </c>
@@ -16893,7 +16894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1089</v>
       </c>
@@ -16934,7 +16935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1089</v>
       </c>
@@ -16975,7 +16976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1089</v>
       </c>
@@ -17016,7 +17017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1089</v>
       </c>
@@ -17057,7 +17058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>1089</v>
       </c>
@@ -17098,7 +17099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>1089</v>
       </c>
@@ -17139,7 +17140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>1089</v>
       </c>
@@ -17180,7 +17181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1089</v>
       </c>
@@ -17221,7 +17222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1089</v>
       </c>
@@ -17262,7 +17263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1089</v>
       </c>
@@ -17303,7 +17304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1089</v>
       </c>
@@ -17344,7 +17345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>1089</v>
       </c>
@@ -17385,7 +17386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>1089</v>
       </c>
@@ -17426,7 +17427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>1089</v>
       </c>
@@ -17467,7 +17468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1089</v>
       </c>
@@ -17508,7 +17509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1089</v>
       </c>
@@ -17549,7 +17550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>1089</v>
       </c>
@@ -17590,7 +17591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1089</v>
       </c>
@@ -17631,7 +17632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>1089</v>
       </c>
@@ -17672,7 +17673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1089</v>
       </c>
@@ -17713,7 +17714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>1089</v>
       </c>
@@ -17754,7 +17755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>1089</v>
       </c>
@@ -17795,7 +17796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>1089</v>
       </c>
@@ -17836,7 +17837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>1089</v>
       </c>
@@ -17877,7 +17878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>1089</v>
       </c>
@@ -17918,7 +17919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>1089</v>
       </c>
@@ -17959,7 +17960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>1187</v>
       </c>
@@ -18000,7 +18001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1187</v>
       </c>
@@ -18041,7 +18042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>1187</v>
       </c>
@@ -18082,7 +18083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>1187</v>
       </c>
@@ -18123,7 +18124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>1187</v>
       </c>
@@ -18164,7 +18165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>1187</v>
       </c>
@@ -18205,7 +18206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>1187</v>
       </c>
@@ -18246,7 +18247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>1187</v>
       </c>
@@ -18287,7 +18288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>1187</v>
       </c>
@@ -18328,7 +18329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>1187</v>
       </c>
@@ -18369,7 +18370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>1187</v>
       </c>
@@ -18410,7 +18411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>1187</v>
       </c>
@@ -18451,7 +18452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>1187</v>
       </c>
@@ -18492,7 +18493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>1187</v>
       </c>
@@ -18533,7 +18534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>1187</v>
       </c>
@@ -18574,7 +18575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>1187</v>
       </c>
@@ -18615,7 +18616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>1187</v>
       </c>
@@ -18656,7 +18657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>1187</v>
       </c>
@@ -18697,7 +18698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>1187</v>
       </c>
@@ -18738,7 +18739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>1187</v>
       </c>
@@ -18779,7 +18780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>1187</v>
       </c>
@@ -18820,7 +18821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>1187</v>
       </c>
@@ -18861,7 +18862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>1187</v>
       </c>
@@ -18902,7 +18903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>1187</v>
       </c>
@@ -18943,7 +18944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>1187</v>
       </c>
@@ -18984,7 +18985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>1187</v>
       </c>
@@ -19025,7 +19026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>1187</v>
       </c>
@@ -19066,7 +19067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>1187</v>
       </c>
@@ -19107,7 +19108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>1187</v>
       </c>
@@ -19148,7 +19149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>1187</v>
       </c>
@@ -19189,7 +19190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>1187</v>
       </c>
@@ -19230,7 +19231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>1187</v>
       </c>
@@ -19271,7 +19272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>1187</v>
       </c>
@@ -19312,7 +19313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>1284</v>
       </c>
@@ -19353,7 +19354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>1284</v>
       </c>
@@ -19394,7 +19395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>1284</v>
       </c>
@@ -19435,7 +19436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>1284</v>
       </c>
@@ -19476,7 +19477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>1284</v>
       </c>
@@ -19517,7 +19518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>1284</v>
       </c>
@@ -19558,7 +19559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>1284</v>
       </c>
@@ -19599,7 +19600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>1284</v>
       </c>
@@ -19640,7 +19641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>1284</v>
       </c>
@@ -19681,7 +19682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>1284</v>
       </c>
@@ -19722,7 +19723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>1284</v>
       </c>
@@ -19763,7 +19764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>1284</v>
       </c>
@@ -19804,7 +19805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>1284</v>
       </c>
@@ -19845,7 +19846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>1284</v>
       </c>
@@ -19886,7 +19887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>1284</v>
       </c>
@@ -19927,7 +19928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>1284</v>
       </c>
@@ -19968,7 +19969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>1284</v>
       </c>
@@ -20009,7 +20010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>1284</v>
       </c>
@@ -20050,7 +20051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>1284</v>
       </c>
@@ -20091,7 +20092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>1284</v>
       </c>
@@ -20132,7 +20133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>1284</v>
       </c>
@@ -20173,7 +20174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>1284</v>
       </c>
@@ -20214,7 +20215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>1284</v>
       </c>
@@ -20255,7 +20256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>1346</v>
       </c>
@@ -20296,7 +20297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>1346</v>
       </c>
@@ -20337,7 +20338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>1346</v>
       </c>
@@ -20378,7 +20379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>1346</v>
       </c>
@@ -20419,7 +20420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>1346</v>
       </c>
@@ -20460,7 +20461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1346</v>
       </c>
@@ -20501,7 +20502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1346</v>
       </c>
@@ -20542,7 +20543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1346</v>
       </c>
@@ -20583,7 +20584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>1346</v>
       </c>
@@ -20624,7 +20625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>1346</v>
       </c>
@@ -20665,7 +20666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1346</v>
       </c>
@@ -20706,7 +20707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1346</v>
       </c>
@@ -20747,7 +20748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>1346</v>
       </c>
@@ -20788,7 +20789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>1346</v>
       </c>
@@ -20829,7 +20830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>1346</v>
       </c>
@@ -20870,7 +20871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>1346</v>
       </c>
@@ -20911,7 +20912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>1346</v>
       </c>
@@ -20952,7 +20953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1346</v>
       </c>
@@ -20993,7 +20994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="376" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>1346</v>
       </c>
@@ -21034,7 +21035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>1346</v>
       </c>
@@ -21075,7 +21076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>1346</v>
       </c>
@@ -21116,7 +21117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>1346</v>
       </c>
@@ -21157,7 +21158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>1346</v>
       </c>
@@ -21198,7 +21199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>1346</v>
       </c>
@@ -21239,7 +21240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>1346</v>
       </c>
@@ -21280,7 +21281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>1346</v>
       </c>
@@ -21321,7 +21322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>1346</v>
       </c>
@@ -21362,7 +21363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>1346</v>
       </c>
@@ -21403,7 +21404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>1346</v>
       </c>
@@ -21444,7 +21445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>1346</v>
       </c>
@@ -21485,7 +21486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>1346</v>
       </c>
@@ -21526,7 +21527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>1346</v>
       </c>
@@ -21567,7 +21568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>1346</v>
       </c>
@@ -21608,7 +21609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>1346</v>
       </c>
@@ -21649,7 +21650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>1346</v>
       </c>
@@ -21690,7 +21691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>1447</v>
       </c>
@@ -21731,7 +21732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>1447</v>
       </c>
@@ -21772,7 +21773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>1447</v>
       </c>
@@ -21813,7 +21814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>1447</v>
       </c>
@@ -21854,7 +21855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>1447</v>
       </c>
@@ -21895,7 +21896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>1447</v>
       </c>
@@ -21936,7 +21937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>1447</v>
       </c>
@@ -21977,7 +21978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="400" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>1447</v>
       </c>
@@ -22018,7 +22019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>1447</v>
       </c>
@@ -22059,7 +22060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>1447</v>
       </c>
@@ -22100,7 +22101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>1447</v>
       </c>
@@ -22141,7 +22142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>1447</v>
       </c>
@@ -22182,7 +22183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="405" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>1447</v>
       </c>
@@ -22223,7 +22224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>1447</v>
       </c>
@@ -22264,7 +22265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="407" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>1447</v>
       </c>
@@ -22305,7 +22306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>1447</v>
       </c>
@@ -22346,7 +22347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>1447</v>
       </c>
@@ -22387,7 +22388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>1447</v>
       </c>
@@ -22428,7 +22429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>1447</v>
       </c>
@@ -22469,7 +22470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>1447</v>
       </c>
@@ -22510,7 +22511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>1447</v>
       </c>
@@ -22551,7 +22552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>1447</v>
       </c>
@@ -22592,7 +22593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>1447</v>
       </c>
@@ -22633,7 +22634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>1447</v>
       </c>
@@ -22674,7 +22675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>1447</v>
       </c>
@@ -22715,7 +22716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>1447</v>
       </c>
@@ -22756,7 +22757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>1447</v>
       </c>
@@ -22797,7 +22798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>1522</v>
       </c>
@@ -22838,7 +22839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="421" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>1522</v>
       </c>
@@ -22879,7 +22880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>1522</v>
       </c>
@@ -22920,7 +22921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>1522</v>
       </c>
@@ -22961,7 +22962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="424" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>1522</v>
       </c>
@@ -23002,7 +23003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>1522</v>
       </c>
@@ -23043,7 +23044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>1522</v>
       </c>
@@ -23084,7 +23085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>1522</v>
       </c>
@@ -23125,7 +23126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>1522</v>
       </c>
@@ -23166,7 +23167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>1522</v>
       </c>
@@ -23207,7 +23208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>1522</v>
       </c>
@@ -23248,7 +23249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>1522</v>
       </c>
@@ -23289,7 +23290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>1522</v>
       </c>
@@ -23330,7 +23331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>1522</v>
       </c>
@@ -23371,7 +23372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>1522</v>
       </c>
@@ -23412,7 +23413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>1522</v>
       </c>
@@ -23453,7 +23454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>1522</v>
       </c>
@@ -23494,7 +23495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>1522</v>
       </c>
@@ -23535,7 +23536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>1522</v>
       </c>
@@ -23576,7 +23577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>1522</v>
       </c>
@@ -23617,7 +23618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>1522</v>
       </c>
@@ -23658,7 +23659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>1522</v>
       </c>
@@ -23699,7 +23700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>1522</v>
       </c>
@@ -23740,7 +23741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>1522</v>
       </c>
@@ -23781,7 +23782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>1522</v>
       </c>
@@ -23822,7 +23823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>1522</v>
       </c>
@@ -23863,7 +23864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>1522</v>
       </c>
@@ -23904,7 +23905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="447" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>1522</v>
       </c>
@@ -23945,7 +23946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>1522</v>
       </c>
@@ -23986,7 +23987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>1522</v>
       </c>
@@ -24027,7 +24028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="450" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>1522</v>
       </c>
@@ -24068,7 +24069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>1522</v>
       </c>
@@ -24109,7 +24110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>1601</v>
       </c>
@@ -24150,7 +24151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>1601</v>
       </c>
@@ -24191,7 +24192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>1601</v>
       </c>
@@ -24232,7 +24233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>1601</v>
       </c>
@@ -24273,7 +24274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>1601</v>
       </c>
@@ -24314,7 +24315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>1601</v>
       </c>
@@ -24355,7 +24356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>1601</v>
       </c>
@@ -24396,7 +24397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>1601</v>
       </c>
@@ -24437,7 +24438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>1601</v>
       </c>
@@ -24478,7 +24479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>1601</v>
       </c>
@@ -24519,7 +24520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>1601</v>
       </c>
@@ -24560,7 +24561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>1601</v>
       </c>
@@ -24601,7 +24602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>1601</v>
       </c>
@@ -24642,7 +24643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>1601</v>
       </c>
@@ -24683,7 +24684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>1601</v>
       </c>
@@ -24724,7 +24725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="467" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>1601</v>
       </c>
@@ -24765,7 +24766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="468" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>1601</v>
       </c>
@@ -24806,7 +24807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>1601</v>
       </c>
@@ -24847,7 +24848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="470" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>1601</v>
       </c>
@@ -24888,7 +24889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="471" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>1601</v>
       </c>
@@ -24929,7 +24930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="472" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>1601</v>
       </c>
@@ -24970,7 +24971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>1601</v>
       </c>
@@ -25011,7 +25012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="474" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>1601</v>
       </c>
@@ -25052,7 +25053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="475" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>1601</v>
       </c>
@@ -25093,7 +25094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>1601</v>
       </c>
@@ -25134,7 +25135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>1601</v>
       </c>
@@ -25175,7 +25176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="478" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>1601</v>
       </c>
@@ -25216,7 +25217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>1601</v>
       </c>
@@ -25257,7 +25258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>1677</v>
       </c>
@@ -25298,7 +25299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>1677</v>
       </c>
@@ -25339,7 +25340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>1677</v>
       </c>
@@ -25380,7 +25381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>1677</v>
       </c>
@@ -25421,7 +25422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>1677</v>
       </c>
@@ -25462,7 +25463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="485" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>1677</v>
       </c>
@@ -25503,7 +25504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>1677</v>
       </c>
@@ -25544,7 +25545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>1677</v>
       </c>
@@ -25585,7 +25586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="488" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>1677</v>
       </c>
@@ -25626,7 +25627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="489" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>1677</v>
       </c>
@@ -25667,7 +25668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>1677</v>
       </c>
@@ -25708,7 +25709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="491" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>1677</v>
       </c>
@@ -25749,7 +25750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>1677</v>
       </c>
@@ -25790,7 +25791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>1677</v>
       </c>
@@ -25831,7 +25832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>1677</v>
       </c>
@@ -25872,7 +25873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>1677</v>
       </c>
@@ -25913,7 +25914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>1677</v>
       </c>
@@ -25954,7 +25955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>1677</v>
       </c>
@@ -25995,7 +25996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="498" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>1677</v>
       </c>
@@ -26036,7 +26037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="499" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>1677</v>
       </c>
@@ -26077,7 +26078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>1677</v>
       </c>
@@ -26118,7 +26119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>1677</v>
       </c>
